--- a/outputs/486-17.xlsx
+++ b/outputs/486-17.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="33">
   <si>
     <t xml:space="preserve">Datum verzending</t>
   </si>
@@ -28,49 +28,97 @@
     <t xml:space="preserve">020210120</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 20</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210107</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 07</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210104</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 04</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210225</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 25</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210222</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 22</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210224</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 24</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210219</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 19</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210223</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 23</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210218</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 02 18</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210108</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 08</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210105</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 05</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210106</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 06</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210119</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 19</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210125</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 25</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210126</t>
   </si>
   <si>
+    <t xml:space="preserve">2021 01 26</t>
+  </si>
+  <si>
     <t xml:space="preserve">020210112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 01 12</t>
   </si>
 </sst>
 </file>
@@ -162,20 +210,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,1149 +435,1023 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">DATE(MID(A2,2,4),MID(A2,6,2),MID(A2,8,2))</f>
-        <v>44216</v>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <f aca="false">DATE(MID(A3,2,4),MID(A3,6,2),MID(A3,8,2))</f>
-        <v>44216</v>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">DATE(MID(A4,2,4),MID(A4,6,2),MID(A4,8,2))</f>
-        <v>44203</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">DATE(MID(A5,2,4),MID(A5,6,2),MID(A5,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">DATE(MID(A6,2,4),MID(A6,6,2),MID(A6,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <f aca="false">DATE(MID(A7,2,4),MID(A7,6,2),MID(A7,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <f aca="false">DATE(MID(A8,2,4),MID(A8,6,2),MID(A8,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <f aca="false">DATE(MID(A9,2,4),MID(A9,6,2),MID(A9,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <f aca="false">DATE(MID(A10,2,4),MID(A10,6,2),MID(A10,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <f aca="false">DATE(MID(A11,2,4),MID(A11,6,2),MID(A11,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <f aca="false">DATE(MID(A12,2,4),MID(A12,6,2),MID(A12,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <f aca="false">DATE(MID(A13,2,4),MID(A13,6,2),MID(A13,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <f aca="false">DATE(MID(A14,2,4),MID(A14,6,2),MID(A14,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <f aca="false">DATE(MID(A15,2,4),MID(A15,6,2),MID(A15,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <f aca="false">DATE(MID(A16,2,4),MID(A16,6,2),MID(A16,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <f aca="false">DATE(MID(A17,2,4),MID(A17,6,2),MID(A17,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <f aca="false">DATE(MID(A18,2,4),MID(A18,6,2),MID(A18,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <f aca="false">DATE(MID(A19,2,4),MID(A19,6,2),MID(A19,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <f aca="false">DATE(MID(A20,2,4),MID(A20,6,2),MID(A20,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <f aca="false">DATE(MID(A21,2,4),MID(A21,6,2),MID(A21,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <f aca="false">DATE(MID(A22,2,4),MID(A22,6,2),MID(A22,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <f aca="false">DATE(MID(A23,2,4),MID(A23,6,2),MID(A23,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <f aca="false">DATE(MID(A24,2,4),MID(A24,6,2),MID(A24,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <f aca="false">DATE(MID(A25,2,4),MID(A25,6,2),MID(A25,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <f aca="false">DATE(MID(A26,2,4),MID(A26,6,2),MID(A26,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <f aca="false">DATE(MID(A27,2,4),MID(A27,6,2),MID(A27,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <f aca="false">DATE(MID(A28,2,4),MID(A28,6,2),MID(A28,8,2))</f>
-        <v>44245</v>
+        <v>17</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <f aca="false">DATE(MID(A29,2,4),MID(A29,6,2),MID(A29,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <f aca="false">DATE(MID(A30,2,4),MID(A30,6,2),MID(A30,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <f aca="false">DATE(MID(A31,2,4),MID(A31,6,2),MID(A31,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <f aca="false">DATE(MID(A32,2,4),MID(A32,6,2),MID(A32,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <f aca="false">DATE(MID(A33,2,4),MID(A33,6,2),MID(A33,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <f aca="false">DATE(MID(A34,2,4),MID(A34,6,2),MID(A34,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <f aca="false">DATE(MID(A35,2,4),MID(A35,6,2),MID(A35,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <f aca="false">DATE(MID(A36,2,4),MID(A36,6,2),MID(A36,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <f aca="false">DATE(MID(A37,2,4),MID(A37,6,2),MID(A37,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <f aca="false">DATE(MID(A38,2,4),MID(A38,6,2),MID(A38,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <f aca="false">DATE(MID(A39,2,4),MID(A39,6,2),MID(A39,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <f aca="false">DATE(MID(A40,2,4),MID(A40,6,2),MID(A40,8,2))</f>
-        <v>44245</v>
+        <v>17</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <f aca="false">DATE(MID(A41,2,4),MID(A41,6,2),MID(A41,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <f aca="false">DATE(MID(A42,2,4),MID(A42,6,2),MID(A42,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <f aca="false">DATE(MID(A43,2,4),MID(A43,6,2),MID(A43,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <f aca="false">DATE(MID(A44,2,4),MID(A44,6,2),MID(A44,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <f aca="false">DATE(MID(A45,2,4),MID(A45,6,2),MID(A45,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <f aca="false">DATE(MID(A46,2,4),MID(A46,6,2),MID(A46,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <f aca="false">DATE(MID(A47,2,4),MID(A47,6,2),MID(A47,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <f aca="false">DATE(MID(A48,2,4),MID(A48,6,2),MID(A48,8,2))</f>
-        <v>44204</v>
+        <v>19</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <f aca="false">DATE(MID(A49,2,4),MID(A49,6,2),MID(A49,8,2))</f>
-        <v>44201</v>
+        <v>21</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <f aca="false">DATE(MID(A50,2,4),MID(A50,6,2),MID(A50,8,2))</f>
-        <v>44204</v>
+        <v>19</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <f aca="false">DATE(MID(A51,2,4),MID(A51,6,2),MID(A51,8,2))</f>
-        <v>44203</v>
+        <v>3</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <f aca="false">DATE(MID(A52,2,4),MID(A52,6,2),MID(A52,8,2))</f>
-        <v>44202</v>
+        <v>23</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <f aca="false">DATE(MID(A53,2,4),MID(A53,6,2),MID(A53,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <f aca="false">DATE(MID(A54,2,4),MID(A54,6,2),MID(A54,8,2))</f>
-        <v>44204</v>
+        <v>19</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <f aca="false">DATE(MID(A55,2,4),MID(A55,6,2),MID(A55,8,2))</f>
-        <v>44215</v>
+        <v>25</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <f aca="false">DATE(MID(A56,2,4),MID(A56,6,2),MID(A56,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="1" t="n">
-        <f aca="false">DATE(MID(A57,2,4),MID(A57,6,2),MID(A57,8,2))</f>
-        <v>44221</v>
+        <v>27</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="1" t="n">
-        <f aca="false">DATE(MID(A58,2,4),MID(A58,6,2),MID(A58,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="1" t="n">
-        <f aca="false">DATE(MID(A59,2,4),MID(A59,6,2),MID(A59,8,2))</f>
-        <v>44222</v>
+        <v>29</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60" s="1" t="n">
-        <f aca="false">DATE(MID(A60,2,4),MID(A60,6,2),MID(A60,8,2))</f>
-        <v>44208</v>
+        <v>31</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="1" t="n">
-        <f aca="false">DATE(MID(A61,2,4),MID(A61,6,2),MID(A61,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B62" s="1" t="n">
-        <f aca="false">DATE(MID(A62,2,4),MID(A62,6,2),MID(A62,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="1" t="n">
-        <f aca="false">DATE(MID(A63,2,4),MID(A63,6,2),MID(A63,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" s="1" t="n">
-        <f aca="false">DATE(MID(A64,2,4),MID(A64,6,2),MID(A64,8,2))</f>
-        <v>44245</v>
+        <v>17</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="1" t="n">
-        <f aca="false">DATE(MID(A65,2,4),MID(A65,6,2),MID(A65,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66" s="1" t="n">
-        <f aca="false">DATE(MID(A66,2,4),MID(A66,6,2),MID(A66,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="1" t="n">
-        <f aca="false">DATE(MID(A67,2,4),MID(A67,6,2),MID(A67,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68" s="1" t="n">
-        <f aca="false">DATE(MID(A68,2,4),MID(A68,6,2),MID(A68,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="1" t="n">
-        <f aca="false">DATE(MID(A69,2,4),MID(A69,6,2),MID(A69,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70" s="1" t="n">
-        <f aca="false">DATE(MID(A70,2,4),MID(A70,6,2),MID(A70,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="1" t="n">
-        <f aca="false">DATE(MID(A71,2,4),MID(A71,6,2),MID(A71,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <f aca="false">DATE(MID(A72,2,4),MID(A72,6,2),MID(A72,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <f aca="false">DATE(MID(A73,2,4),MID(A73,6,2),MID(A73,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="1" t="n">
-        <f aca="false">DATE(MID(A74,2,4),MID(A74,6,2),MID(A74,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B75" s="1" t="n">
-        <f aca="false">DATE(MID(A75,2,4),MID(A75,6,2),MID(A75,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" s="1" t="n">
-        <f aca="false">DATE(MID(A76,2,4),MID(A76,6,2),MID(A76,8,2))</f>
-        <v>44245</v>
+        <v>17</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <f aca="false">DATE(MID(A77,2,4),MID(A77,6,2),MID(A77,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <f aca="false">DATE(MID(A78,2,4),MID(A78,6,2),MID(A78,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" s="1" t="n">
-        <f aca="false">DATE(MID(A79,2,4),MID(A79,6,2),MID(A79,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <f aca="false">DATE(MID(A80,2,4),MID(A80,6,2),MID(A80,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <f aca="false">DATE(MID(A81,2,4),MID(A81,6,2),MID(A81,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="1" t="n">
-        <f aca="false">DATE(MID(A82,2,4),MID(A82,6,2),MID(A82,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" s="1" t="n">
-        <f aca="false">DATE(MID(A83,2,4),MID(A83,6,2),MID(A83,8,2))</f>
-        <v>44245</v>
+        <v>17</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" s="1" t="n">
-        <f aca="false">DATE(MID(A84,2,4),MID(A84,6,2),MID(A84,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B85" s="1" t="n">
-        <f aca="false">DATE(MID(A85,2,4),MID(A85,6,2),MID(A85,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <f aca="false">DATE(MID(A86,2,4),MID(A86,6,2),MID(A86,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <f aca="false">DATE(MID(A87,2,4),MID(A87,6,2),MID(A87,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <f aca="false">DATE(MID(A88,2,4),MID(A88,6,2),MID(A88,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <f aca="false">DATE(MID(A89,2,4),MID(A89,6,2),MID(A89,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <f aca="false">DATE(MID(A90,2,4),MID(A90,6,2),MID(A90,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <f aca="false">DATE(MID(A91,2,4),MID(A91,6,2),MID(A91,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <f aca="false">DATE(MID(A92,2,4),MID(A92,6,2),MID(A92,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <f aca="false">DATE(MID(A93,2,4),MID(A93,6,2),MID(A93,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <f aca="false">DATE(MID(A94,2,4),MID(A94,6,2),MID(A94,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B95" s="1" t="n">
-        <f aca="false">DATE(MID(A95,2,4),MID(A95,6,2),MID(A95,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="1" t="n">
-        <f aca="false">DATE(MID(A96,2,4),MID(A96,6,2),MID(A96,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <f aca="false">DATE(MID(A97,2,4),MID(A97,6,2),MID(A97,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B98" s="1" t="n">
-        <f aca="false">DATE(MID(A98,2,4),MID(A98,6,2),MID(A98,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <f aca="false">DATE(MID(A102,2,4),MID(A102,6,2),MID(A102,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <f aca="false">DATE(MID(A103,2,4),MID(A103,6,2),MID(A103,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B104" s="1" t="n">
-        <f aca="false">DATE(MID(A104,2,4),MID(A104,6,2),MID(A104,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <f aca="false">DATE(MID(A105,2,4),MID(A105,6,2),MID(A105,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="1" t="n">
-        <f aca="false">DATE(MID(A106,2,4),MID(A106,6,2),MID(A106,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <f aca="false">DATE(MID(A107,2,4),MID(A107,6,2),MID(A107,8,2))</f>
-        <v>44200</v>
+        <v>5</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B108" s="1" t="n">
-        <f aca="false">DATE(MID(A108,2,4),MID(A108,6,2),MID(A108,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <f aca="false">DATE(MID(A109,2,4),MID(A109,6,2),MID(A109,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <f aca="false">DATE(MID(A110,2,4),MID(A110,6,2),MID(A110,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B111" s="1" t="n">
-        <f aca="false">DATE(MID(A111,2,4),MID(A111,6,2),MID(A111,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B112" s="1" t="n">
-        <f aca="false">DATE(MID(A112,2,4),MID(A112,6,2),MID(A112,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B113" s="1" t="n">
-        <f aca="false">DATE(MID(A113,2,4),MID(A113,6,2),MID(A113,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B114" s="1" t="n">
-        <f aca="false">DATE(MID(A114,2,4),MID(A114,6,2),MID(A114,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B115" s="1" t="n">
-        <f aca="false">DATE(MID(A115,2,4),MID(A115,6,2),MID(A115,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" s="1" t="n">
-        <f aca="false">DATE(MID(A116,2,4),MID(A116,6,2),MID(A116,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B117" s="1" t="n">
-        <f aca="false">DATE(MID(A117,2,4),MID(A117,6,2),MID(A117,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B118" s="1" t="n">
-        <f aca="false">DATE(MID(A118,2,4),MID(A118,6,2),MID(A118,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B119" s="1" t="n">
-        <f aca="false">DATE(MID(A119,2,4),MID(A119,6,2),MID(A119,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B120" s="1" t="n">
-        <f aca="false">DATE(MID(A120,2,4),MID(A120,6,2),MID(A120,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B121" s="1" t="n">
-        <f aca="false">DATE(MID(A121,2,4),MID(A121,6,2),MID(A121,8,2))</f>
-        <v>44251</v>
+        <v>11</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B122" s="1" t="n">
-        <f aca="false">DATE(MID(A122,2,4),MID(A122,6,2),MID(A122,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B123" s="1" t="n">
-        <f aca="false">DATE(MID(A123,2,4),MID(A123,6,2),MID(A123,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B124" s="1" t="n">
-        <f aca="false">DATE(MID(A124,2,4),MID(A124,6,2),MID(A124,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B125" s="1" t="n">
-        <f aca="false">DATE(MID(A125,2,4),MID(A125,6,2),MID(A125,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B126" s="1" t="n">
-        <f aca="false">DATE(MID(A126,2,4),MID(A126,6,2),MID(A126,8,2))</f>
-        <v>44249</v>
+        <v>9</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B127" s="1" t="n">
-        <f aca="false">DATE(MID(A127,2,4),MID(A127,6,2),MID(A127,8,2))</f>
-        <v>44250</v>
+        <v>15</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B128" s="1" t="n">
-        <f aca="false">DATE(MID(A128,2,4),MID(A128,6,2),MID(A128,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B129" s="1" t="n">
-        <f aca="false">DATE(MID(A129,2,4),MID(A129,6,2),MID(A129,8,2))</f>
-        <v>44252</v>
+        <v>7</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B130" s="1" t="n">
-        <f aca="false">DATE(MID(A130,2,4),MID(A130,6,2),MID(A130,8,2))</f>
-        <v>44246</v>
+        <v>13</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/486-17.xlsx
+++ b/outputs/486-17.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="17">
   <si>
     <t xml:space="preserve">Datum verzending</t>
   </si>
@@ -28,106 +28,59 @@
     <t xml:space="preserve">020210120</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 20</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210107</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 07</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210104</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 04</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210225</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 25</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210222</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 22</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210224</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 24</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210219</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 19</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210223</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 23</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210218</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 02 18</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210108</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 08</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210105</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 05</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210106</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 06</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210119</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 19</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210125</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 25</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210126</t>
   </si>
   <si>
-    <t xml:space="preserve">2021 01 26</t>
-  </si>
-  <si>
     <t xml:space="preserve">020210112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021 01 12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\ mm\ dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -223,7 +176,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,776 +388,776 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
+      <c r="B2" s="3" t="n">
+        <v>44216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="n">
+        <v>44216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>44203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>44245</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>44245</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>44204</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>44201</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>44204</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>44203</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>44202</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>44204</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>44215</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>44221</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>44222</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>44208</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>44245</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>44245</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>44245</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1224,234 +1177,234 @@
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>44251</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>44252</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>44246</v>
       </c>
     </row>
   </sheetData>
